--- a/laporan_surat_keluar.xlsx
+++ b/laporan_surat_keluar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,7 +464,157 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Ditolak</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>002\MS\V1\2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>cayaaaa</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>mtk</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>004\MS\V1\2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>cayaa</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>membuattuas</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ditolak</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>008\MS\V1\2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cayaa</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>tugas</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>008\MS\V1\2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>kepala sekolah</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>tugas</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>010\MS\V1\2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>fitian</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Tugas</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>011\MS\V1\2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>kepala sekolah</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>tugas</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Disetujui</t>
         </is>
       </c>
     </row>
